--- a/questionnaire_templates/043_physical_fitness_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/043_physical_fitness_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This questionnaire is designed to assess your physical fitness.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -551,7 +555,11 @@
           <t>General Questions</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please answer these questions to the best of your ability.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -574,7 +582,11 @@
           <t>Medical History</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Have you ever had a major medical condition or illness?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medical_history_2</t>
+          <t>exercise_questions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Previous Medical History</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Exercise Questions</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How often do you engage in physical exercise?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>exercise_questions</t>
+          <t>physical_activity_level</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Exercise Questions</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Physical Activity Level</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How physically active are you?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>exercise_frequency</t>
+          <t>height_weight</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Height and Weight</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide your height and weight.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>physical_activity_level</t>
+          <t>body_mass_index</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Physical Activity Level</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Body Mass Index</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What is your body mass index?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>height_weight</t>
+          <t>resting_heart_rate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height and Weight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Resting Heart Rate</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>What is your resting heart rate?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>body_mass_index</t>
+          <t>blood_pressure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Body Mass Index</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Blood Pressure</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Have you had high blood pressure issues?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>height_weight_2</t>
+          <t>exercise_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Height and Weight</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Exercise Frequency</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How frequent do you exercise?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,343 +785,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>height_weight_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Resting Heart Rate</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Height Weight 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide your height and weight.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>blood_pressure</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Blood Pressure</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>exercise_frequency_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>exercise_frequency_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>exercise_frequency_4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>exercise_frequency_5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>exercise_frequency_6</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>exercise_frequency_7</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>exercise_frequency_8</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>exercise_frequency_9</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>exercise_frequency_10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>exercise_frequency_11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>exercise_frequency_12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>exercise_frequency_13</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>exercise_frequency_14</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Exercise Frequency</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +820,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1194,34 +916,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_history_2_choices</t>
+          <t>exercise_questions_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_history_2_choices</t>
+          <t>exercise_questions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1233,29 +955,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>exercise_questions_choices</t>
+          <t>physical_activity_level_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1267,29 +989,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>physical_activity_level_choices</t>
+          <t>height_weight_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1023,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>height_weight_choices</t>
+          <t>body_mass_index_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>underweight</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Underweight</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1057,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1352,554 +1074,163 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>overweight</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Overweight</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>height_weight_2_choices</t>
+          <t>resting_heart_rate_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>height_weight_2_choices</t>
+          <t>resting_heart_rate_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>resting_heart_rate_choices</t>
+          <t>blood_pressure_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>resting_heart_rate_choices</t>
+          <t>blood_pressure_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>blood_pressure_choices</t>
+          <t>exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>blood_pressure_choices</t>
+          <t>exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>exercise_frequency_2_choices</t>
+          <t>exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>exercise_frequency_2_choices</t>
+          <t>height_weight_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>exercise_frequency_3_choices</t>
+          <t>height_weight_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>exercise_frequency_3_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>exercise_frequency_4_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>exercise_frequency_4_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>exercise_frequency_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>exercise_frequency_5_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>exercise_frequency_6_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>exercise_frequency_6_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>exercise_frequency_7_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>exercise_frequency_7_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>exercise_frequency_8_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>exercise_frequency_8_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>exercise_frequency_9_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>exercise_frequency_9_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>exercise_frequency_10_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>exercise_frequency_10_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>exercise_frequency_11_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>exercise_frequency_11_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>exercise_frequency_12_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>exercise_frequency_12_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>exercise_frequency_13_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>exercise_frequency_13_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>exercise_frequency_14_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>exercise_frequency_14_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
